--- a/Table_S13.xlsx
+++ b/Table_S13.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S13_TF_family" sheetId="1" r:id="Rd267ef78c6544e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S13_TF_family" sheetId="1" r:id="Rb46e893d441b47a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -337,7 +337,7 @@
   <x:sheetData>
     <x:row r="1" s="13" customFormat="1" ht="36" customHeight="1">
       <x:c r="A1" s="22" t="str">
-        <x:v>Table S13. Natural seed-variant TF-family motif summary.</x:v>
+        <x:v>Table S13. Natural seed-variant transcription-factor-family motif summary.</x:v>
       </x:c>
       <x:c r="B1" s="1" t="n"/>
       <x:c r="C1" s="1" t="n"/>
